--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487004_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487004_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7224</v>
+        <v>4.429</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8839</v>
+        <v>3.7091</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8385</v>
+        <v>0.7199</v>
       </c>
       <c r="G2" t="n">
         <v>4.1926</v>
@@ -610,13 +610,13 @@
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8809</v>
+        <v>-0.1742</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1857</v>
+        <v>-0.3605</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3048</v>
+        <v>0.1862</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3655</v>
+        <v>3.0056</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8641</v>
+        <v>4.6821</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4986</v>
+        <v>-1.6765</v>
       </c>
       <c r="G3" t="n">
         <v>0.2144</v>
@@ -688,13 +688,13 @@
         <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4743</v>
+        <v>0.1144</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4725</v>
+        <v>0.2904</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0018</v>
+        <v>-0.1761</v>
       </c>
       <c r="V3" t="n">
         <v>1.6501</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6656</v>
+        <v>2.7974</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9413</v>
+        <v>3.0731</v>
       </c>
       <c r="F4" t="n">
         <v>-0.2757</v>
@@ -766,10 +766,10 @@
         <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.492</v>
+        <v>-0.3603</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0272</v>
+        <v>0.1045</v>
       </c>
       <c r="U4" t="n">
         <v>-0.4648</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5645</v>
+        <v>1.8298</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7015</v>
+        <v>0.9964</v>
       </c>
       <c r="F5" t="n">
-        <v>0.863</v>
+        <v>0.8334</v>
       </c>
       <c r="G5" t="n">
         <v>2.2232</v>
@@ -844,13 +844,13 @@
         <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4645</v>
+        <v>-0.2702</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4066</v>
+        <v>-0.2985</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0579</v>
+        <v>0.0283</v>
       </c>
       <c r="V5" t="n">
         <v>0.6982</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. KNOWLES</t>
+          <t>E. MOURE COLOMBO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9104</v>
+        <v>1.2598</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8687</v>
+        <v>0.4891</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9583</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.575</v>
+        <v>0.7145</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0066</v>
+        <v>-1.5669</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5816</v>
+        <v>2.2813</v>
       </c>
       <c r="J6" t="n">
-        <v>1.474</v>
+        <v>0.4348</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6847</v>
+        <v>-0.9859</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7893</v>
+        <v>1.4208</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.899</v>
+        <v>0.2796</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6913</v>
+        <v>-0.581</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2077</v>
+        <v>0.8606</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.4107</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>1.2321</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5703</v>
+        <v>-0.4465</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5651</v>
+        <v>-0.186</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0052</v>
+        <v>-0.2604</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0563</v>
+        <v>-0.2402</v>
       </c>
       <c r="W6" t="n">
         <v>0.2402</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2965</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. MOURE COLOMBO</t>
+          <t>D. KNOWLES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6521</v>
+        <v>0.8932</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1481</v>
+        <v>2.059</v>
       </c>
       <c r="F7" t="n">
-        <v>0.504</v>
+        <v>-1.1658</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7145</v>
+        <v>0.575</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5669</v>
+        <v>-0.0066</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2813</v>
+        <v>0.5816</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4348</v>
+        <v>1.474</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9859</v>
+        <v>0.6847</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4208</v>
+        <v>0.7893</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2796</v>
+        <v>-0.899</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.581</v>
+        <v>-0.6913</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8606</v>
+        <v>-0.2077</v>
       </c>
       <c r="P7" t="n">
-        <v>1.2321</v>
+        <v>0.8214</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.4107</v>
       </c>
       <c r="R7" t="n">
         <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0542</v>
+        <v>0.5531</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.527</v>
+        <v>0.7554</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5272</v>
+        <v>-0.2023</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2402</v>
+        <v>-1.0563</v>
       </c>
       <c r="W7" t="n">
         <v>0.2402</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4805</v>
+        <v>-1.2965</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2501</v>
+        <v>-0.1546</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3073</v>
+        <v>-1.2414</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0572</v>
+        <v>1.0868</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2622</v>
@@ -1078,13 +1078,13 @@
         <v>0.2053</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1933</v>
+        <v>-0.0978</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2635</v>
+        <v>-0.1976</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0702</v>
+        <v>0.0998</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4687</v>
+        <v>-0.4813</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2919</v>
+        <v>-0.5713</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1767</v>
+        <v>0.09</v>
       </c>
       <c r="G9" t="n">
         <v>0.5872000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>2.0534</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5889</v>
+        <v>-0.6015</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1857</v>
+        <v>-0.4651</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4032</v>
+        <v>-0.1364</v>
       </c>
       <c r="V9" t="n">
         <v>-0.4669</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6504</v>
+        <v>-3.0911</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9645</v>
+        <v>-1.3756</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6858</v>
+        <v>-1.7155</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9704</v>
@@ -1234,13 +1234,13 @@
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7326</v>
+        <v>-0.1733</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4611</v>
+        <v>0.1278</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2715</v>
+        <v>-0.3011</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5367</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7812</v>
+        <v>-3.4402</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3966</v>
+        <v>-1.0557</v>
       </c>
       <c r="F11" t="n">
         <v>-2.3845</v>
@@ -1312,10 +1312,10 @@
         <v>0.8214</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0926</v>
+        <v>-0.7516</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7905</v>
+        <v>-0.4495</v>
       </c>
       <c r="U11" t="n">
         <v>-0.3021</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.7301</v>
+        <v>7.0476</v>
       </c>
       <c r="E12" t="n">
-        <v>9.4473</v>
+        <v>10.7648</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7169</v>
+        <v>-3.7172</v>
       </c>
       <c r="G12" t="n">
         <v>11.6558</v>
@@ -1390,10 +1390,10 @@
         <v>12.3206</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.5254</v>
+        <v>-2.2079</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.9965</v>
+        <v>-0.6791000000000001</v>
       </c>
       <c r="U12" t="n">
         <v>-1.5289</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. KALU</t>
+          <t>G. MARTINEZ RIVERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6388</v>
+        <v>4.2136</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6124</v>
+        <v>5.1219</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0263</v>
+        <v>-0.9083</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2024</v>
+        <v>1.9164</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8071</v>
+        <v>1.9402</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.6047</v>
+        <v>-0.0238</v>
       </c>
       <c r="J13" t="n">
-        <v>2.7376</v>
+        <v>4.3068</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5797</v>
+        <v>3.2416</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1579</v>
+        <v>1.0652</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.5352</v>
+        <v>-2.3904</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7726</v>
+        <v>-1.3014</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.7626</v>
+        <v>-1.089</v>
       </c>
       <c r="P13" t="n">
-        <v>1.0267</v>
+        <v>-0.616</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0534</v>
+        <v>1.4374</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1694</v>
+        <v>0.3157</v>
       </c>
       <c r="T13" t="n">
-        <v>2.6613</v>
+        <v>0.271</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5081</v>
+        <v>0.0447</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2402</v>
+        <v>2.5975</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2402</v>
+        <v>2.5975</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. MARTINEZ RIVERA</t>
+          <t>F. GARRIDO TEBAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.708</v>
+        <v>3.5511</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9127</v>
+        <v>3.457</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2047</v>
+        <v>0.0941</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9164</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9402</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0238</v>
+        <v>0.6974</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3068</v>
+        <v>0.6034</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2416</v>
+        <v>0.6034</v>
       </c>
       <c r="L14" t="n">
-        <v>1.0652</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3904</v>
+        <v>0.003</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3014</v>
+        <v>-0.6943</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.089</v>
+        <v>0.6974</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4374</v>
+        <v>0.2053</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1899</v>
+        <v>-0.2073</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0618</v>
+        <v>-0.093</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2517</v>
+        <v>-0.1143</v>
       </c>
       <c r="V14" t="n">
-        <v>2.5975</v>
+        <v>2.9466</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5975</v>
+        <v>2.9466</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. GARRIDO TEBAN</t>
+          <t>E. KALU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3872</v>
+        <v>2.9948</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3524</v>
+        <v>2.9388</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0348</v>
+        <v>0.056</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.2024</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.09089999999999999</v>
+        <v>1.8071</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6974</v>
+        <v>-1.6047</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6034</v>
+        <v>2.7376</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6034</v>
+        <v>2.5797</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.1579</v>
       </c>
       <c r="M15" t="n">
-        <v>0.003</v>
+        <v>-2.5352</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6943</v>
+        <v>-0.7726</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6974</v>
+        <v>-1.7626</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2053</v>
+        <v>1.0267</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2053</v>
+        <v>2.0534</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3712</v>
+        <v>1.5254</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1976</v>
+        <v>0.9877</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1735</v>
+        <v>0.5377</v>
       </c>
       <c r="V15" t="n">
-        <v>2.9466</v>
+        <v>0.2402</v>
       </c>
       <c r="W15" t="n">
-        <v>2.9466</v>
+        <v>0.2402</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ROKER</t>
+          <t>J. CASTILLO CARRASCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4116</v>
+        <v>-0.4293</v>
       </c>
       <c r="E16" t="n">
-        <v>0.446</v>
+        <v>-0.6136</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8576</v>
+        <v>0.1843</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9552</v>
+        <v>-1.8821</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6131</v>
+        <v>-0.9928</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3422</v>
+        <v>-0.8893</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5967</v>
+        <v>-1.8774</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5573</v>
+        <v>-0.5222</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0395</v>
+        <v>-1.3552</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6415</v>
+        <v>-0.0047</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9442</v>
+        <v>-0.4706</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3027</v>
+        <v>0.4659</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0.2053</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0438</v>
+        <v>0.309</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.124</v>
+        <v>0.0852</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1678</v>
+        <v>0.2238</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5893</v>
+        <v>0.9384</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5893</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CASTILLO CARRASCO</t>
+          <t>A. ROKER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5496</v>
+        <v>-0.6191</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8228</v>
+        <v>0.446</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2732</v>
+        <v>-1.0651</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.8821</v>
+        <v>0.9552</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9928</v>
+        <v>0.6131</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8893</v>
+        <v>0.3422</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.8774</v>
+        <v>1.5967</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5222</v>
+        <v>1.5573</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3552</v>
+        <v>0.0395</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0047</v>
+        <v>-0.6415</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4706</v>
+        <v>-0.9442</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4659</v>
+        <v>0.3027</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2053</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
         <v>0.2053</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1887</v>
+        <v>-0.1637</v>
       </c>
       <c r="T17" t="n">
         <v>-0.124</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3128</v>
+        <v>-0.0396</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9384</v>
+        <v>-0.5893</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2402</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8512</v>
+        <v>-0.7169</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1862</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.665</v>
+        <v>-0.6353</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3595</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2515</v>
+        <v>-0.1172</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1317</v>
+        <v>-0.0271</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1197</v>
+        <v>-0.0901</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2402</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8948</v>
+        <v>-1.0447</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0283</v>
+        <v>-0.1809</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.923</v>
+        <v>-0.8638</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2821</v>
@@ -1936,13 +1936,13 @@
         <v>1.4374</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1286</v>
+        <v>-0.0213</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0699</v>
+        <v>-0.2791</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1985</v>
+        <v>0.2578</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1786</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5067</v>
+        <v>-2.9357</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3652</v>
+        <v>0.4698</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8719</v>
+        <v>-3.4055</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5304</v>
@@ -2014,13 +2014,13 @@
         <v>1.8481</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2638</v>
+        <v>0.8349</v>
       </c>
       <c r="T20" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.1741</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1943</v>
+        <v>0.6607</v>
       </c>
       <c r="V20" t="n">
         <v>-2.0082</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BOIX COLET</t>
+          <t>J. JUANOLA MADERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.0964</v>
+        <v>-5.1688</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.0799</v>
+        <v>-4.0742</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0165</v>
+        <v>-1.0946</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.2304</v>
+        <v>-6.0519</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4597</v>
+        <v>-3.3997</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.7707</v>
+        <v>-2.6522</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.6424</v>
+        <v>-2.7381</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3791</v>
+        <v>-1.9879</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.2633</v>
+        <v>-0.7502</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.588</v>
+        <v>-3.3138</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0807</v>
+        <v>-1.4118</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5074</v>
+        <v>-1.902</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4107</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6427</v>
+        <v>2.2588</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2428</v>
+        <v>0.2857</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1354</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1074</v>
+        <v>0.2007</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6982</v>
+        <v>1.4189</v>
       </c>
       <c r="W21" t="n">
-        <v>0.4805</v>
+        <v>1.6591</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. JUANOLA MADERA</t>
+          <t>J. BOIX COLET</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.1538</v>
+        <v>-5.5751</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.911</v>
+        <v>-3.7661</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2428</v>
+        <v>-1.809</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.0519</v>
+        <v>-5.2304</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.3997</v>
+        <v>-1.4597</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.6522</v>
+        <v>-3.7707</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.7381</v>
+        <v>-2.6424</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.9879</v>
+        <v>-0.3791</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7502</v>
+        <v>-2.2633</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.3138</v>
+        <v>-2.588</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4118</v>
+        <v>-1.0807</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.902</v>
+        <v>-1.5074</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.8214</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2588</v>
+        <v>1.6427</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6994</v>
+        <v>0.7641</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7518</v>
+        <v>0.4492</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0524</v>
+        <v>0.3149</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4189</v>
+        <v>-0.6982</v>
       </c>
       <c r="W22" t="n">
-        <v>1.6591</v>
+        <v>0.4805</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="23">
@@ -2206,25 +2206,25 @@
         <v>-5.7301</v>
       </c>
       <c r="E23" t="n">
-        <v>3.717099999999999</v>
+        <v>3.717100000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.447199999999999</v>
+        <v>-9.4472</v>
       </c>
       <c r="G23" t="n">
         <v>-11.656</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9733000000000001</v>
+        <v>-0.9733000000000003</v>
       </c>
       <c r="I23" t="n">
         <v>-10.6825</v>
       </c>
       <c r="J23" t="n">
-        <v>4.227599999999998</v>
+        <v>4.227600000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>7.6107</v>
+        <v>7.610699999999999</v>
       </c>
       <c r="L23" t="n">
         <v>-3.3831</v>
@@ -2236,7 +2236,7 @@
         <v>-8.584099999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>-7.299400000000001</v>
+        <v>-7.2994</v>
       </c>
       <c r="P23" t="n">
         <v>-1.0269</v>
@@ -2248,13 +2248,13 @@
         <v>11.2937</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5251</v>
+        <v>3.5253</v>
       </c>
       <c r="T23" t="n">
         <v>1.529</v>
       </c>
       <c r="U23" t="n">
-        <v>1.9964</v>
+        <v>1.9963</v>
       </c>
       <c r="V23" t="n">
         <v>3.4271</v>
